--- a/Pipeline/NOTEBOOKS/config.xlsx
+++ b/Pipeline/NOTEBOOKS/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="config"/>
@@ -56,13 +56,13 @@
     <t>Integracion de datos de oleaje</t>
   </si>
   <si>
-    <t>5.clasificacion</t>
+    <t>5.clasificacion_oleaje</t>
   </si>
   <si>
     <t>Clasificacion K-Means del oleaje</t>
   </si>
   <si>
-    <t>6.estudio</t>
+    <t>6.estudio_oleaje</t>
   </si>
   <si>
     <t>Estudio de correlaciones</t>
@@ -74,7 +74,7 @@
     <t>Entrenamiento de modelos</t>
   </si>
   <si>
-    <t>8.comparacion_modelos</t>
+    <t>8.estudio_modelos</t>
   </si>
   <si>
     <t>Comparacion de modelos</t>
@@ -139,7 +139,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,12 +156,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -276,11 +270,11 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,7 +585,7 @@
     <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -599,7 +593,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -639,7 +633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
@@ -671,7 +665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -679,7 +673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -687,7 +681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -695,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>

--- a/Pipeline/NOTEBOOKS/config.xlsx
+++ b/Pipeline/NOTEBOOKS/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="config"/>
@@ -662,7 +662,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">

--- a/Pipeline/NOTEBOOKS/config.xlsx
+++ b/Pipeline/NOTEBOOKS/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="config"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>notebook</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Limpieza global de datos agregados</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>4.oleaje</t>
   </si>
   <si>
@@ -62,28 +59,25 @@
     <t>Clasificacion K-Means del oleaje</t>
   </si>
   <si>
-    <t>6.estudio_oleaje</t>
+    <t>6.estudio_clasificacion</t>
   </si>
   <si>
     <t>Estudio de correlaciones</t>
   </si>
   <si>
-    <t>7.modelos</t>
+    <t>7.modelos_flujo</t>
   </si>
   <si>
     <t>Entrenamiento de modelos</t>
   </si>
   <si>
-    <t>8.estudio_modelos</t>
-  </si>
-  <si>
-    <t>Comparacion de modelos</t>
-  </si>
-  <si>
-    <t>9.graficas</t>
+    <t>8.graficas</t>
   </si>
   <si>
     <t>Graficas y visualizacion</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>parameter</t>
@@ -247,9 +241,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -581,120 +578,120 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="7">
+        <v>24</v>
+      </c>
+      <c r="B3" s="8">
         <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="7">
+        <v>25</v>
+      </c>
+      <c r="B4" s="8">
         <v>7200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="7">
+        <v>26</v>
+      </c>
+      <c r="B5" s="8">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="7">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8">
         <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="7" t="b">
+        <v>28</v>
+      </c>
+      <c r="B7" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="7">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
         <v>-8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="7">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8">
         <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="7">
+        <v>31</v>
+      </c>
+      <c r="B10" s="8">
         <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="7">
+        <v>32</v>
+      </c>
+      <c r="B11" s="8">
         <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="7">
+        <v>33</v>
+      </c>
+      <c r="B12" s="8">
         <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="7">
+        <v>34</v>
+      </c>
+      <c r="B13" s="8">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -710,9 +707,9 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -756,73 +753,73 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
